--- a/data/trans_orig/P36B17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B17-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>150925</t>
+          <t>166555</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132271</t>
+          <t>146367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>188866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>193964</t>
+          <t>211758</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176482</t>
+          <t>191697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211429</t>
+          <t>233200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>344890</t>
+          <t>378313</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316210</t>
+          <t>349327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371769</t>
+          <t>406562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202451</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175617</t>
+          <t>198763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228780</t>
+          <t>249884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>247028</t>
+          <t>268460</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226027</t>
+          <t>246607</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267004</t>
+          <t>290725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>449479</t>
+          <t>490583</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>419234</t>
+          <t>456638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486544</t>
+          <t>525166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>212364</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186629</t>
+          <t>202471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>241615</t>
+          <t>257823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186995</t>
+          <t>199721</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168393</t>
+          <t>180123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205712</t>
+          <t>220543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>399358</t>
+          <t>428639</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>364144</t>
+          <t>392957</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>431219</t>
+          <t>462579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -1064,67 +1064,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>48335</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77027</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>39835</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28836</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>52430</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>5,48%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36546</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>27881</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>48016</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84301</t>
+          <t>88170</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>70685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>116249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>41006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>687184</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>687184</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>687184</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>670840</t>
+          <t>726436</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670840</t>
+          <t>726436</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>670840</t>
+          <t>726436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1302731</t>
+          <t>1413620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1302731</t>
+          <t>1413620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1302731</t>
+          <t>1413620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>201080</t>
+          <t>233162</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>203354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262300</t>
+          <t>263200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>237419</t>
+          <t>267451</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>241389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260340</t>
+          <t>291423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>438499</t>
+          <t>500613</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294865</t>
+          <t>460361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511347</t>
+          <t>537785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>280419</t>
+          <t>321797</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136046</t>
+          <t>288220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>363424</t>
+          <t>358319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>363318</t>
+          <t>403637</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338020</t>
+          <t>376719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>390085</t>
+          <t>430411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>643737</t>
+          <t>725433</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420093</t>
+          <t>682799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>737929</t>
+          <t>767141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>373559</t>
+          <t>391930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>176623</t>
+          <t>357978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486106</t>
+          <t>430662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>303515</t>
+          <t>339168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>278323</t>
+          <t>311362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>330265</t>
+          <t>367651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>677073</t>
+          <t>731098</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>464312</t>
+          <t>687584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>779901</t>
+          <t>783377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72514</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102655</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>112758</t>
+          <t>121780</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140096</t>
+          <t>148718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>265292</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>739883</t>
+          <t>39778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,67 +1894,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>39313</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>27146</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>54574</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>277500</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>33037</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>865056</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956704</t>
+          <t>1069321</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956704</t>
+          <t>1069321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956704</t>
+          <t>1069321</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2149568</t>
+          <t>2118238</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2149568</t>
+          <t>2118238</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2149568</t>
+          <t>2118238</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>187141</t>
+          <t>216696</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161302</t>
+          <t>190200</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215180</t>
+          <t>246059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>401717</t>
+          <t>233330</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240711</t>
+          <t>210406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667106</t>
+          <t>254776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>588857</t>
+          <t>450026</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>422107</t>
+          <t>416087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>930701</t>
+          <t>489283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>239289</t>
+          <t>273215</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207723</t>
+          <t>242314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267676</t>
+          <t>304686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>235909</t>
+          <t>273143</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115564</t>
+          <t>249319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313737</t>
+          <t>299154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>475198</t>
+          <t>546359</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321692</t>
+          <t>505773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>556386</t>
+          <t>586523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>227674</t>
+          <t>254664</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199696</t>
+          <t>223725</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>258330</t>
+          <t>287577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>247245</t>
+          <t>252391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123369</t>
+          <t>224767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>344087</t>
+          <t>279804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>474918</t>
+          <t>507055</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>304179</t>
+          <t>470381</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>569516</t>
+          <t>550677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>49796</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63458</t>
+          <t>69390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36621</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>79908</t>
+          <t>90372</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>70575</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107339</t>
+          <t>114631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>281363</t>
+          <t>299677</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253522</t>
+          <t>274888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310607</t>
+          <t>331075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>347691</t>
+          <t>387409</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>281847</t>
+          <t>359193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>382450</t>
+          <t>414511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>629055</t>
+          <t>687085</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>551043</t>
+          <t>650503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>671779</t>
+          <t>730625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>295475</t>
+          <t>312017</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263942</t>
+          <t>280736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>324142</t>
+          <t>340871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>355851</t>
+          <t>385423</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289588</t>
+          <t>357528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392629</t>
+          <t>413494</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>651325</t>
+          <t>697440</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>571527</t>
+          <t>658455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>695432</t>
+          <t>742358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>255728</t>
+          <t>272879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227675</t>
+          <t>241165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296786</t>
+          <t>301658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>325203</t>
+          <t>271128</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>261885</t>
+          <t>246087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>470590</t>
+          <t>297673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>580932</t>
+          <t>544007</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>514827</t>
+          <t>503193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>752511</t>
+          <t>586655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>64112</t>
+          <t>70436</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46862</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83305</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>48369</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63794</t>
+          <t>72995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>112481</t>
+          <t>126798</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>103643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138584</t>
+          <t>151759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>49826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57304</t>
+          <t>68593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925996</t>
+          <t>989217</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925996</t>
+          <t>989217</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925996</t>
+          <t>989217</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1090103</t>
+          <t>1116320</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1090103</t>
+          <t>1116320</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1090103</t>
+          <t>1116320</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2016099</t>
+          <t>2105537</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2016099</t>
+          <t>2105537</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2016099</t>
+          <t>2105537</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>820511</t>
+          <t>916089</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>617626</t>
+          <t>860785</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>901733</t>
+          <t>971510</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1180791</t>
+          <t>1099948</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1009632</t>
+          <t>1050639</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1640024</t>
+          <t>1150676</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2001302</t>
+          <t>2016037</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1799354</t>
+          <t>1948160</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2427695</t>
+          <t>2091280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1017634</t>
+          <t>1129153</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>758741</t>
+          <t>1068265</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1118444</t>
+          <t>1184929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1202105</t>
+          <t>1330663</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1283771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1303542</t>
+          <t>1384538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2219740</t>
+          <t>2459816</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1935533</t>
+          <t>2385739</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2373973</t>
+          <t>2546057</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1069325</t>
+          <t>1148391</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>810350</t>
+          <t>1091079</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1167781</t>
+          <t>1215568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1062957</t>
+          <t>1062408</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>889481</t>
+          <t>1005997</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1215676</t>
+          <t>1111050</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2132282</t>
+          <t>2210799</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1876472</t>
+          <t>2122245</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2314624</t>
+          <t>2299833</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>227669</t>
+          <t>246721</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>182622</t>
+          <t>209791</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>271996</t>
+          <t>285239</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>180400</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>127510</t>
+          <t>158063</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>187599</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>389448</t>
+          <t>427120</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>326619</t>
+          <t>379351</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>440276</t>
+          <t>472869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>320293</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1087171</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>66691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>363673</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>114201</t>
+          <t>116279</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1198403</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
